--- a/MyPaper/paper/文獻回顧整理.xlsx
+++ b/MyPaper/paper/文獻回顧整理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_LTY\Lee_Tsung_Yu\MyPaper\paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D421274-84E3-4BCA-B7B2-EE765320C7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B4279C-6C98-43AC-9F2F-AA5C6C31F181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4ECBDD3-FD53-446C-9F84-5864BFD1C340}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Fuel consumption monitoring chart for marine voyage data:
  A combined deep learning and time series method</t>
@@ -115,8 +115,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>2024.06.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Study On the Current Status of Illegal Wildlife Trade Based on
+ARIMA And Logistic Regression Modelling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Zishuo Liu, 
+Yanli Zhang
+Senyuan Ma, </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve"> Employ linear combination of the predicted values from ARIMAX and LSTM-FCN,
- to get the optimal schedule for vessel maintainance</t>
+ to get the optimal schedule for vessel maintainance.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022.xx.xx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2262EB45-EFF4-492E-88FF-5963FAEEBD38}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="65.5546875" style="2" customWidth="1"/>
@@ -550,14 +569,14 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
-        <v>2022</v>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
@@ -591,6 +610,17 @@
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
